--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20261007_235742.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20261007_235742.xlsx
@@ -5700,7 +5700,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20261007_235742.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20261007_235742.xlsx
@@ -5700,7 +5700,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
